--- a/grid-core/expected/out/daily_kpi.xlsx
+++ b/grid-core/expected/out/daily_kpi.xlsx
@@ -12127,7 +12127,7 @@
         <v>Generated</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-08-04T03:21:34.719Z</v>
+        <v>2026-08-04T08:04:00.225Z</v>
       </c>
     </row>
     <row r="10">
